--- a/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,39; 5,01</t>
+          <t>1,68; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,61</t>
+          <t>0,86; 3,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,69</t>
+          <t>0,89; 3,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,66</t>
+          <t>1,4; 4,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,31</t>
+          <t>2,42; 7,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,57; 7,13</t>
+          <t>2,67; 7,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,65</t>
+          <t>2,33; 7,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,86</t>
+          <t>1,03; 3,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,28</t>
+          <t>2,36; 5,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,33</t>
+          <t>1,89; 4,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,31</t>
+          <t>1,79; 4,34</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,69</t>
+          <t>1,58; 3,57</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,63</t>
+          <t>0,78; 3,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,66</t>
+          <t>1,28; 4,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,62</t>
+          <t>1,73; 5,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,92</t>
+          <t>0,47; 3,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,16</t>
+          <t>2,78; 7,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,71; 9,04</t>
+          <t>3,61; 8,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,52</t>
+          <t>2,13; 6,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,97</t>
+          <t>0,81; 2,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,81</t>
+          <t>2,01; 4,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,93</t>
+          <t>2,76; 5,9</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,21</t>
+          <t>2,34; 5,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,66</t>
+          <t>0,74; 2,69</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,35; 7,13</t>
+          <t>3,4; 7,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,33</t>
+          <t>3,63; 7,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 7,04</t>
+          <t>2,97; 7,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,16</t>
+          <t>0,41; 3,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 11,67</t>
+          <t>2,95; 10,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,84</t>
+          <t>2,99; 8,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,29</t>
+          <t>0,7; 5,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 5,15</t>
+          <t>0,41; 6,06</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,04</t>
+          <t>3,84; 7,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,0; 7,14</t>
+          <t>3,93; 7,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,95</t>
+          <t>2,7; 6,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,81</t>
+          <t>0,55; 2,97</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,71</t>
+          <t>3,38; 5,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 7,36</t>
+          <t>4,6; 7,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,22</t>
+          <t>3,0; 5,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,32</t>
+          <t>1,47; 3,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 7,51</t>
+          <t>3,93; 7,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,12</t>
+          <t>5,81; 9,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,92</t>
+          <t>3,82; 6,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,59</t>
+          <t>0,69; 2,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,8</t>
+          <t>3,88; 5,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,9</t>
+          <t>5,49; 7,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,5</t>
+          <t>3,63; 5,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,71</t>
+          <t>1,33; 2,73</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 13,73</t>
+          <t>6,86; 13,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,12</t>
+          <t>4,73; 9,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,96</t>
+          <t>3,67; 8,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,33</t>
+          <t>1,45; 4,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,67; 12,01</t>
+          <t>6,86; 12,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 9,41</t>
+          <t>5,53; 9,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,16; 8,63</t>
+          <t>5,14; 8,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,33</t>
+          <t>2,04; 4,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,55; 11,96</t>
+          <t>7,52; 11,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,74; 8,74</t>
+          <t>5,69; 8,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,52</t>
+          <t>4,94; 7,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,9</t>
+          <t>2,0; 3,73</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,56</t>
+          <t>4,29; 10,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,44</t>
+          <t>1,56; 6,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,26; 10,58</t>
+          <t>4,35; 10,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 4,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,96</t>
+          <t>4,43; 7,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,62</t>
+          <t>3,79; 6,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,81</t>
+          <t>2,34; 4,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 5,96</t>
+          <t>2,22; 6,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,14</t>
+          <t>4,48; 6,91</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,12</t>
+          <t>3,69; 6,05</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,45</t>
+          <t>3,18; 5,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 4,86</t>
+          <t>1,86; 5,02</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,64</t>
+          <t>4,0; 5,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,51</t>
+          <t>4,08; 5,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 5,1</t>
+          <t>3,59; 5,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,66</t>
+          <t>1,51; 2,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 6,88</t>
+          <t>5,14; 6,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,04</t>
+          <t>5,46; 7,11</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 5,33</t>
+          <t>3,86; 5,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,02</t>
+          <t>1,82; 3,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,81; 6,01</t>
+          <t>4,83; 5,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,96; 6,09</t>
+          <t>4,95; 6,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,97; 4,99</t>
+          <t>3,95; 4,93</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,71</t>
+          <t>1,84; 2,66</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6569; 23726</t>
+          <t>7955; 24908</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3803; 15788</t>
+          <t>3755; 15454</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3835; 15804</t>
+          <t>3789; 15937</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7436; 23215</t>
+          <t>6989; 21258</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7311; 22348</t>
+          <t>7407; 22144</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8083; 22429</t>
+          <t>8407; 24944</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8089; 22946</t>
+          <t>8043; 24467</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4722; 17171</t>
+          <t>4591; 17258</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18374; 41185</t>
+          <t>18417; 41471</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14176; 32532</t>
+          <t>14236; 32494</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14729; 33328</t>
+          <t>13826; 33531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15148; 34842</t>
+          <t>14902; 33654</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2938; 13283</t>
+          <t>2857; 13640</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5181; 19389</t>
+          <t>5345; 19180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6508; 20969</t>
+          <t>6461; 20829</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2054; 17569</t>
+          <t>2100; 15794</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9795; 26554</t>
+          <t>10315; 27458</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12465; 30346</t>
+          <t>12115; 29938</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8635; 24139</t>
+          <t>7872; 23282</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3101; 11183</t>
+          <t>3046; 11171</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15463; 35445</t>
+          <t>14780; 35232</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21497; 44583</t>
+          <t>20797; 44382</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18023; 38727</t>
+          <t>17398; 39985</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6913; 21917</t>
+          <t>6146; 22189</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18087; 38512</t>
+          <t>18384; 37855</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23058; 45884</t>
+          <t>22709; 45187</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15127; 36373</t>
+          <t>15352; 36151</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2419; 20948</t>
+          <t>2692; 21075</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5008; 19582</t>
+          <t>4942; 18078</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8308; 23008</t>
+          <t>7787; 22558</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1224; 10455</t>
+          <t>1158; 9863</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>491; 8443</t>
+          <t>676; 9929</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25632; 49839</t>
+          <t>27157; 51040</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35484; 63328</t>
+          <t>34832; 62361</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19101; 40605</t>
+          <t>18455; 41126</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4203; 23247</t>
+          <t>4525; 24567</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41141; 70563</t>
+          <t>41735; 71682</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53396; 84983</t>
+          <t>53098; 84234</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>31977; 59710</t>
+          <t>34306; 61766</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15254; 34326</t>
+          <t>15209; 35837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>27799; 53654</t>
+          <t>28037; 54683</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>45147; 77178</t>
+          <t>44304; 75394</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31042; 56800</t>
+          <t>31363; 56520</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6517; 25146</t>
+          <t>6684; 25536</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75185; 113153</t>
+          <t>75637; 115189</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>104234; 151496</t>
+          <t>105219; 150490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70212; 108091</t>
+          <t>71344; 109199</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25985; 54397</t>
+          <t>26632; 54843</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24276; 47661</t>
+          <t>23810; 48365</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24285; 46486</t>
+          <t>24083; 46419</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23708; 49239</t>
+          <t>22701; 50094</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6821; 20484</t>
+          <t>6876; 21171</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37743; 67953</t>
+          <t>38809; 68955</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41408; 71263</t>
+          <t>41896; 71067</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37853; 63328</t>
+          <t>37738; 64565</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16766; 36076</t>
+          <t>16982; 34975</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68919; 109155</t>
+          <t>68701; 105533</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72786; 110718</t>
+          <t>72091; 108117</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67334; 101787</t>
+          <t>66886; 102754</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27158; 50971</t>
+          <t>26086; 48749</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12672; 31277</t>
+          <t>12722; 30750</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4076; 17091</t>
+          <t>4130; 16288</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12177; 30268</t>
+          <t>12448; 30772</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 11533</t>
+          <t>0; 11062</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>53277; 86646</t>
+          <t>55091; 87402</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44073; 73119</t>
+          <t>41842; 70340</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26380; 51815</t>
+          <t>25197; 51153</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16395; 45007</t>
+          <t>16787; 45249</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>73020; 109993</t>
+          <t>69090; 106460</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51621; 83848</t>
+          <t>50643; 82905</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41915; 74286</t>
+          <t>43394; 73757</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>19005; 48049</t>
+          <t>18371; 49545</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>134033; 183962</t>
+          <t>130325; 182809</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>139863; 187762</t>
+          <t>139027; 191687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>123060; 171734</t>
+          <t>121007; 170070</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49502; 89262</t>
+          <t>50665; 91407</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>174018; 231698</t>
+          <t>173285; 234536</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>191859; 249027</t>
+          <t>193070; 251427</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>138161; 187408</t>
+          <t>135480; 186277</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>64633; 107163</t>
+          <t>64608; 108768</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>319082; 398238</t>
+          <t>320135; 395088</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>344742; 423179</t>
+          <t>343533; 421614</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>273068; 343204</t>
+          <t>271569; 339396</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>128458; 187108</t>
+          <t>126959; 183299</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,26</t>
+          <t>1,6; 5,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,53</t>
+          <t>0,78; 3,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,72</t>
+          <t>0,86; 3,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,26</t>
+          <t>1,33; 4,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,24</t>
+          <t>2,62; 7,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,93</t>
+          <t>2,77; 7,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,09</t>
+          <t>2,28; 6,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 3,88</t>
+          <t>1,27; 3,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,32</t>
+          <t>2,37; 5,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,32</t>
+          <t>1,89; 4,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,34</t>
+          <t>1,86; 4,46</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,57</t>
+          <t>1,52; 3,44</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,73</t>
+          <t>0,77; 3,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,61</t>
+          <t>1,19; 4,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,58</t>
+          <t>1,82; 5,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,52</t>
+          <t>0,72; 3,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,4</t>
+          <t>2,9; 7,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,91</t>
+          <t>3,85; 9,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,29</t>
+          <t>2,23; 6,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,97</t>
+          <t>1,17; 3,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,78</t>
+          <t>2,09; 4,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,9</t>
+          <t>2,81; 5,76</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 5,38</t>
+          <t>2,41; 5,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,69</t>
+          <t>1,19; 3,14</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,4; 7,01</t>
+          <t>3,35; 6,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,63; 7,21</t>
+          <t>3,72; 7,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 7,0</t>
+          <t>3,02; 6,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,18</t>
+          <t>1,05; 4,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,95; 10,77</t>
+          <t>2,97; 11,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 8,67</t>
+          <t>3,23; 9,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,94</t>
+          <t>0,66; 6,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,06</t>
+          <t>0,88; 5,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,21</t>
+          <t>3,75; 7,17</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,03</t>
+          <t>3,96; 6,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,02</t>
+          <t>2,74; 6,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,97</t>
+          <t>1,29; 3,79</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,38; 5,8</t>
+          <t>3,35; 5,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 7,3</t>
+          <t>4,55; 7,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,4</t>
+          <t>2,89; 5,39</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,47</t>
+          <t>2,05; 4,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,93; 7,66</t>
+          <t>3,99; 7,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 9,89</t>
+          <t>5,95; 10,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,89</t>
+          <t>3,88; 7,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,63</t>
+          <t>1,78; 3,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 5,91</t>
+          <t>3,89; 5,85</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 7,85</t>
+          <t>5,53; 7,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,56</t>
+          <t>3,54; 5,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,73</t>
+          <t>2,1; 3,57</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 13,93</t>
+          <t>6,99; 14,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,73; 9,11</t>
+          <t>4,82; 9,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,09</t>
+          <t>3,71; 7,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,48</t>
+          <t>1,97; 5,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 12,18</t>
+          <t>6,66; 12,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,53; 9,38</t>
+          <t>5,66; 9,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,8</t>
+          <t>4,87; 8,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,2</t>
+          <t>2,91; 5,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,52; 11,56</t>
+          <t>7,44; 11,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,53</t>
+          <t>5,77; 8,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,6</t>
+          <t>4,86; 7,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,73</t>
+          <t>2,78; 4,73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,29; 10,38</t>
+          <t>4,31; 10,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,13</t>
+          <t>1,7; 6,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 10,76</t>
+          <t>4,25; 11,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,74</t>
+          <t>0,0; 4,35</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,02</t>
+          <t>4,42; 6,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,36</t>
+          <t>3,81; 6,46</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,75</t>
+          <t>2,34; 4,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,0</t>
+          <t>2,69; 6,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,91</t>
+          <t>4,7; 7,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,05</t>
+          <t>3,67; 6,03</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,41</t>
+          <t>3,12; 5,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,02</t>
+          <t>2,34; 5,24</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 5,61</t>
+          <t>4,11; 5,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,08; 5,62</t>
+          <t>4,09; 5,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,59; 5,05</t>
+          <t>3,69; 5,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,73</t>
+          <t>2,06; 3,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,96</t>
+          <t>5,18; 6,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,46; 7,11</t>
+          <t>5,37; 7,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 5,3</t>
+          <t>3,85; 5,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,07</t>
+          <t>2,66; 3,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,83; 5,96</t>
+          <t>4,87; 6,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,95; 6,07</t>
+          <t>4,95; 6,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,95; 4,93</t>
+          <t>3,96; 4,93</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 2,66</t>
+          <t>2,48; 3,28</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22793</t>
+          <t>24522</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7955; 24908</t>
+          <t>7602; 24729</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3755; 15454</t>
+          <t>3397; 14908</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3789; 15937</t>
+          <t>3697; 15284</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6989; 21258</t>
+          <t>7233; 22894</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7407; 22144</t>
+          <t>8014; 23703</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8407; 24944</t>
+          <t>8725; 24138</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8043; 24467</t>
+          <t>7870; 23842</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4591; 17258</t>
+          <t>6182; 18531</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18417; 41471</t>
+          <t>18503; 41224</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14236; 32494</t>
+          <t>14181; 32544</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13826; 33531</t>
+          <t>14361; 34513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14902; 33654</t>
+          <t>15686; 35400</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>9179</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12089</t>
+          <t>17555</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2857; 13640</t>
+          <t>2820; 12344</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5345; 19180</t>
+          <t>4965; 18331</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6461; 20829</t>
+          <t>6795; 20252</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2100; 15794</t>
+          <t>3471; 18371</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10315; 27458</t>
+          <t>10761; 27816</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12115; 29938</t>
+          <t>12924; 31526</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7872; 23282</t>
+          <t>8254; 22986</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3046; 11171</t>
+          <t>4885; 14926</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>14780; 35232</t>
+          <t>15397; 35268</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20797; 44382</t>
+          <t>21163; 43313</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17398; 39985</t>
+          <t>17904; 38411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6146; 22189</t>
+          <t>10670; 28149</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>15238</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18384; 37855</t>
+          <t>18092; 37745</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22709; 45187</t>
+          <t>23281; 45198</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15352; 36151</t>
+          <t>15590; 35463</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2692; 21075</t>
+          <t>4925; 19555</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4942; 18078</t>
+          <t>4978; 18766</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7787; 22558</t>
+          <t>8399; 24198</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1158; 9863</t>
+          <t>1094; 10078</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>676; 9929</t>
+          <t>1615; 10730</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>27157; 51040</t>
+          <t>26585; 50787</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34832; 62361</t>
+          <t>35063; 61369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18455; 41126</t>
+          <t>18715; 40980</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4525; 24567</t>
+          <t>8383; 24674</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>33839</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>16006</t>
+          <t>21472</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>55311</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41735; 71682</t>
+          <t>41357; 71094</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>53098; 84234</t>
+          <t>52536; 85434</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34306; 61766</t>
+          <t>33047; 61586</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15209; 35837</t>
+          <t>23204; 49220</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>28037; 54683</t>
+          <t>28493; 53119</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44304; 75394</t>
+          <t>45371; 76929</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31363; 56520</t>
+          <t>31854; 57651</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6684; 25536</t>
+          <t>15176; 31256</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75637; 115189</t>
+          <t>75929; 114118</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>105219; 150490</t>
+          <t>105951; 152599</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71344; 109199</t>
+          <t>69576; 107057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>26632; 54843</t>
+          <t>41747; 70896</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12390</t>
+          <t>18494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24514</t>
+          <t>33336</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>36904</t>
+          <t>51830</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23810; 48365</t>
+          <t>24267; 49069</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24083; 46419</t>
+          <t>24549; 46924</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22701; 50094</t>
+          <t>22956; 48296</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6876; 21171</t>
+          <t>11169; 30010</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38809; 68955</t>
+          <t>37672; 67885</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41896; 71067</t>
+          <t>42872; 72716</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37738; 64565</t>
+          <t>35723; 62968</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>16982; 34975</t>
+          <t>23995; 43551</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68701; 105533</t>
+          <t>67887; 104041</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72091; 108117</t>
+          <t>73101; 110369</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66886; 102754</t>
+          <t>65705; 103468</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>26086; 48749</t>
+          <t>38620; 65671</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>26143</t>
+          <t>34343</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>29350</t>
+          <t>37196</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12722; 30750</t>
+          <t>12777; 30125</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4130; 16288</t>
+          <t>4508; 16236</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12448; 30772</t>
+          <t>12165; 31594</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 11062</t>
+          <t>0; 9998</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>55091; 87402</t>
+          <t>55031; 85827</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41842; 70340</t>
+          <t>42057; 71408</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25197; 51153</t>
+          <t>25188; 49338</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16787; 45249</t>
+          <t>22512; 51763</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>69090; 106460</t>
+          <t>72351; 111425</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>50643; 82905</t>
+          <t>50286; 82678</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>43394; 73757</t>
+          <t>42557; 74224</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18371; 49545</t>
+          <t>24939; 55903</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68585</t>
+          <t>87773</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>84715</t>
+          <t>113880</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>153301</t>
+          <t>201652</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>130325; 182809</t>
+          <t>134064; 185889</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>139027; 191687</t>
+          <t>139429; 190120</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121007; 170070</t>
+          <t>124114; 174284</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50665; 91407</t>
+          <t>70355; 108206</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>173285; 234536</t>
+          <t>174628; 231020</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>193070; 251427</t>
+          <t>189736; 251860</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>135480; 186277</t>
+          <t>135320; 186917</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>64608; 108768</t>
+          <t>95658; 138602</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>320135; 395088</t>
+          <t>322692; 397651</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>343533; 421614</t>
+          <t>343925; 420090</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>271569; 339396</t>
+          <t>272234; 339025</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>126959; 183299</t>
+          <t>173842; 230467</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
